--- a/01-Constants-audit/Model Audit v1.xlsx
+++ b/01-Constants-audit/Model Audit v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\finance-portfolio\01-Constants-audit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2820FD-63D2-423D-92A9-AB952C7EA24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004154D7-2AA3-4A01-8BF0-8D3AEEBD16F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P&amp;L" sheetId="1" r:id="rId1"/>
@@ -986,7 +986,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1042,6 +1042,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1694,7 +1695,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="5">
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="5">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1716,26 +1717,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" customWidth="1"/>
+    <col min="5" max="6" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.1796875" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="18.140625" customWidth="1"/>
+    <col min="11" max="11" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1794,7 +1795,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>44927</v>
       </c>
@@ -1870,7 +1871,7 @@
         <v>-2100</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>44958</v>
       </c>
@@ -1946,7 +1947,7 @@
         <v>-2034.9399999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>44986</v>
       </c>
@@ -2022,7 +2023,7 @@
         <v>-1943.96</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45017</v>
       </c>
@@ -2098,7 +2099,7 @@
         <v>-1826.5450000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45047</v>
       </c>
@@ -2174,7 +2175,7 @@
         <v>-1709.7749999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45078</v>
       </c>
@@ -2250,7 +2251,7 @@
         <v>-1608.6800000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>45108</v>
       </c>
@@ -2326,7 +2327,7 @@
         <v>-1491.96875</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>45139</v>
       </c>
@@ -2402,7 +2403,7 @@
         <v>-1483.4050000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>45170</v>
       </c>
@@ -2478,7 +2479,7 @@
         <v>-1543.2099999999991</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>45200</v>
       </c>
@@ -2554,7 +2555,7 @@
         <v>-1511.5587500000001</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>45231</v>
       </c>
@@ -2630,7 +2631,7 @@
         <v>-1045.5774999999994</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>45261</v>
       </c>
@@ -2706,7 +2707,7 @@
         <v>-1240.9412499999999</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>45292</v>
       </c>
@@ -2782,7 +2783,7 @@
         <v>-1013.4837499999994</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>45323</v>
       </c>
@@ -2858,7 +2859,7 @@
         <v>-472.54750000000058</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>45352</v>
       </c>
@@ -2934,7 +2935,7 @@
         <v>-1292.5175000000017</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>45383</v>
       </c>
@@ -3010,7 +3011,7 @@
         <v>-763.54875000000175</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>45413</v>
       </c>
@@ -3086,7 +3087,7 @@
         <v>-768.92124999999942</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>45444</v>
       </c>
@@ -3162,7 +3163,7 @@
         <v>-911.8849999999984</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>45474</v>
       </c>
@@ -3238,7 +3239,7 @@
         <v>-984.5099999999984</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>45505</v>
       </c>
@@ -3314,7 +3315,7 @@
         <v>-675.73749999999927</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>45536</v>
       </c>
@@ -3390,7 +3391,7 @@
         <v>-456.18624999999884</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>45566</v>
       </c>
@@ -3466,7 +3467,7 @@
         <v>-402.58499999999913</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>45597</v>
       </c>
@@ -3542,7 +3543,7 @@
         <v>-40.8125</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>45627</v>
       </c>
@@ -3618,7 +3619,7 @@
         <v>-41.647499999999127</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>45658</v>
       </c>
@@ -3694,7 +3695,7 @@
         <v>-205.88999999999942</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>45689</v>
       </c>
@@ -3770,7 +3771,7 @@
         <v>-181.55625000000146</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>45717</v>
       </c>
@@ -3846,7 +3847,7 @@
         <v>485.70624999999927</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>45748</v>
       </c>
@@ -3922,7 +3923,7 @@
         <v>-104.79249999999956</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>45778</v>
       </c>
@@ -3998,7 +3999,7 @@
         <v>510.77375000000029</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>45809</v>
       </c>
@@ -4074,7 +4075,7 @@
         <v>1749.2249999999985</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>45839</v>
       </c>
@@ -4150,7 +4151,7 @@
         <v>642.03874999999971</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>45870</v>
       </c>
@@ -4226,7 +4227,7 @@
         <v>505.13624999999956</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>45901</v>
       </c>
@@ -4302,7 +4303,7 @@
         <v>132.01250000000073</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>45931</v>
       </c>
@@ -4378,7 +4379,7 @@
         <v>1056.6412500000006</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>45962</v>
       </c>
@@ -4454,7 +4455,7 @@
         <v>857.45000000000073</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>45992</v>
       </c>
@@ -4530,7 +4531,7 @@
         <v>1020.0849999999991</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>46023</v>
       </c>
@@ -4605,6 +4606,12 @@
         <f>Q37-tblPL[[#This Row],[dta]]</f>
         <v>-2076.5849999999991</v>
       </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="I41" s="33"/>
+      <c r="K41" s="33"/>
+      <c r="M41" s="33"/>
+      <c r="S41" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4617,14 +4624,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA66C908-C0F1-432D-927F-1E00FFA05D00}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="61" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -4635,7 +4642,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -4646,7 +4653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -4657,7 +4664,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -4668,7 +4675,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -4679,7 +4686,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -4690,7 +4697,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -4701,7 +4708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>108</v>
       </c>
@@ -4712,7 +4719,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>110</v>
       </c>
@@ -4723,7 +4730,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -4734,7 +4741,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>114</v>
       </c>
@@ -4745,7 +4752,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>116</v>
       </c>
@@ -4756,7 +4763,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -4767,7 +4774,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>200</v>
       </c>
@@ -4789,36 +4796,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49FA2890-9280-4DFA-8B0B-CD61771F3B96}">
   <dimension ref="A1:J112"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="49.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" customWidth="1"/>
-    <col min="4" max="4" width="43.85546875" customWidth="1"/>
-    <col min="5" max="5" width="49.5703125" customWidth="1"/>
-    <col min="6" max="6" width="57.140625" customWidth="1"/>
+    <col min="1" max="1" width="49.54296875" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" customWidth="1"/>
+    <col min="3" max="3" width="51.453125" customWidth="1"/>
+    <col min="4" max="4" width="43.81640625" customWidth="1"/>
+    <col min="5" max="5" width="49.54296875" customWidth="1"/>
+    <col min="6" max="6" width="57.1796875" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="72.42578125" customWidth="1"/>
+    <col min="8" max="8" width="72.453125" customWidth="1"/>
     <col min="9" max="9" width="21" customWidth="1"/>
     <col min="10" max="10" width="99" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>172</v>
       </c>
@@ -4827,7 +4834,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>173</v>
       </c>
@@ -4836,30 +4843,30 @@
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>174</v>
       </c>
       <c r="B7" s="2" cm="1">
-        <f t="array" ref="B7">SUMPRODUCT(--_xlfn.ISFORMULA('P&amp;L'!A2:O38))</f>
-        <v>481</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <f t="array" ref="B7">SUMPRODUCT(--_xlfn.ISFORMULA('P&amp;L'!A2:S38))</f>
+        <v>629</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>175</v>
       </c>
       <c r="B8" s="2">
-        <f>COUNT('P&amp;L'!A2:O38)-B7</f>
+        <f>COUNT('P&amp;L'!A2:S38)-B7</f>
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>176</v>
       </c>
@@ -4873,7 +4880,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1</v>
       </c>
@@ -4890,7 +4897,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2</v>
       </c>
@@ -4907,7 +4914,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>3</v>
       </c>
@@ -4924,18 +4931,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="str">
         <f>COUNTIF(tblConstantsAudit[Cells using],D11)&amp;" constants are tied at "&amp;D11&amp;" uses; ties are shown in table order."</f>
         <v>6 constants are tied at 37 uses; ties are shown in table order.</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>123</v>
       </c>
@@ -4967,7 +4974,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
         <v>133</v>
       </c>
@@ -5002,7 +5009,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>137</v>
       </c>
@@ -5037,7 +5044,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="19" t="s">
         <v>137</v>
       </c>
@@ -5072,7 +5079,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="19" t="s">
         <v>143</v>
       </c>
@@ -5107,7 +5114,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19" t="s">
         <v>147</v>
       </c>
@@ -5142,7 +5149,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="19" t="s">
         <v>207</v>
       </c>
@@ -5177,7 +5184,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="19" t="s">
         <v>208</v>
       </c>
@@ -5212,7 +5219,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="19" t="s">
         <v>209</v>
       </c>
@@ -5247,7 +5254,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="19" t="s">
         <v>210</v>
       </c>
@@ -5282,7 +5289,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="19" t="s">
         <v>160</v>
       </c>
@@ -5307,7 +5314,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="19" t="s">
         <v>164</v>
       </c>
@@ -5332,7 +5339,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="19" t="s">
         <v>211</v>
       </c>
@@ -5357,7 +5364,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="19" t="s">
         <v>212</v>
       </c>
@@ -5382,7 +5389,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="19" t="s">
         <v>213</v>
       </c>
@@ -5407,7 +5414,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="19" t="s">
         <v>214</v>
       </c>
@@ -5432,7 +5439,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="19" t="s">
         <v>150</v>
       </c>
@@ -5457,7 +5464,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="19" t="s">
         <v>220</v>
       </c>
@@ -5487,7 +5494,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="19" t="s">
         <v>223</v>
       </c>
@@ -5517,7 +5524,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="19" t="s">
         <v>225</v>
       </c>
@@ -5547,7 +5554,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="19" t="s">
         <v>227</v>
       </c>
@@ -5572,13 +5579,13 @@
         <v>228</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="25" t="s">
         <v>181</v>
       </c>
@@ -5601,7 +5608,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="27" t="s">
         <v>187</v>
       </c>
@@ -5628,7 +5635,7 @@
         <v>5455.2512500000048</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="27" t="s">
         <v>188</v>
       </c>
@@ -5655,7 +5662,7 @@
         <v>17348.113750000033</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="27" t="s">
         <v>190</v>
       </c>
@@ -5682,7 +5689,7 @@
         <v>-310.0462000000407</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="27" t="s">
         <v>192</v>
       </c>
@@ -5709,7 +5716,7 @@
         <v>32373.41499999995</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="27" t="s">
         <v>193</v>
       </c>
@@ -5736,7 +5743,7 @@
         <v>406130.58500000066</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="27" t="s">
         <v>195</v>
       </c>
@@ -5763,7 +5770,7 @@
         <v>2.1200000017415732E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="27" t="s">
         <v>230</v>
       </c>
@@ -5790,7 +5797,7 @@
         <v>5455.2512500000048</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="27" t="s">
         <v>232</v>
       </c>
@@ -5817,7 +5824,7 @@
         <v>17348.113750000033</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="27" t="s">
         <v>235</v>
       </c>
@@ -5832,7 +5839,7 @@
       <c r="F48" s="17"/>
       <c r="G48" s="16"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="27" t="s">
         <v>238</v>
       </c>
@@ -5859,7 +5866,7 @@
         <v>32373.41499999995</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="27" t="s">
         <v>197</v>
       </c>
@@ -5883,12 +5890,12 @@
         <v>32373.415000000008</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="28" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="27" t="s">
         <v>241</v>
       </c>
@@ -5897,7 +5904,7 @@
         <v>91898.794999999984</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="27" t="s">
         <v>242</v>
       </c>
@@ -5906,7 +5913,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="27" t="s">
         <v>243</v>
       </c>
@@ -5915,7 +5922,7 @@
         <v>22974.698749999996</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="27" t="s">
         <v>244</v>
       </c>
@@ -5924,7 +5931,7 @@
         <v>22974.698749999996</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="27" t="s">
         <v>90</v>
       </c>
@@ -5933,7 +5940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="27" t="s">
         <v>245</v>
       </c>
@@ -5942,7 +5949,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="27" t="s">
         <v>246</v>
       </c>
@@ -5951,7 +5958,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="27" t="s">
         <v>247</v>
       </c>
@@ -5960,22 +5967,22 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>30</v>
       </c>
@@ -5984,7 +5991,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>31</v>
       </c>
@@ -5993,7 +6000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>32</v>
       </c>
@@ -6002,7 +6009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>33</v>
       </c>
@@ -6010,17 +6017,17 @@
         <v>34</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>37</v>
       </c>
@@ -6040,7 +6047,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>43</v>
       </c>
@@ -6060,7 +6067,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>45</v>
       </c>
@@ -6080,7 +6087,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>47</v>
       </c>
@@ -6103,7 +6110,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>50</v>
       </c>
@@ -6123,7 +6130,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>52</v>
       </c>
@@ -6146,7 +6153,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>55</v>
       </c>
@@ -6166,7 +6173,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>57</v>
       </c>
@@ -6189,7 +6196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>60</v>
       </c>
@@ -6212,7 +6219,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>62</v>
       </c>
@@ -6235,7 +6242,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>64</v>
       </c>
@@ -6255,7 +6262,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>65</v>
       </c>
@@ -6278,7 +6285,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>67</v>
       </c>
@@ -6298,7 +6305,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>68</v>
       </c>
@@ -6318,7 +6325,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>70</v>
       </c>
@@ -6341,7 +6348,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>73</v>
       </c>
@@ -6357,12 +6364,12 @@
       <c r="E90" s="7"/>
       <c r="F90" s="7"/>
     </row>
-    <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
         <v>75</v>
       </c>
@@ -6376,7 +6383,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>78</v>
       </c>
@@ -6392,7 +6399,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>79</v>
       </c>
@@ -6405,7 +6412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>80</v>
       </c>
@@ -6421,7 +6428,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>81</v>
       </c>
@@ -6434,7 +6441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>82</v>
       </c>
@@ -6450,7 +6457,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="32.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>83</v>
       </c>
@@ -6466,7 +6473,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>84</v>
       </c>
@@ -6482,7 +6489,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>85</v>
       </c>
@@ -6495,12 +6502,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="6" t="s">
         <v>87</v>
       </c>
@@ -6520,7 +6527,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>91</v>
       </c>
@@ -6545,7 +6552,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>104</v>
       </c>
@@ -6570,7 +6577,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>105</v>
       </c>
@@ -6595,7 +6602,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>92</v>
       </c>
@@ -6620,7 +6627,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>93</v>
       </c>
@@ -6645,7 +6652,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>94</v>
       </c>
@@ -6670,7 +6677,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>106</v>
       </c>
@@ -6685,25 +6692,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E8BFE6D-9A62-4637-AEC4-EC35F5927826}">
-  <dimension ref="A1:P38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P46"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6750,7 +6757,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>44927</v>
       </c>
@@ -6794,7 +6801,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>44958</v>
       </c>
@@ -6838,7 +6845,7 @@
         <v>75700</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>44986</v>
       </c>
@@ -6882,7 +6889,7 @@
         <v>66095.179999999993</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45017</v>
       </c>
@@ -6926,7 +6933,7 @@
         <v>56763.3</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45047</v>
       </c>
@@ -6970,7 +6977,7 @@
         <v>47780.67</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45078</v>
       </c>
@@ -7014,7 +7021,7 @@
         <v>39150.54</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>45108</v>
       </c>
@@ -7058,7 +7065,7 @@
         <v>30824.51</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>45139</v>
       </c>
@@ -7102,7 +7109,7 @@
         <v>22848.66</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>45170</v>
       </c>
@@ -7146,7 +7153,7 @@
         <v>14898.45</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>45200</v>
       </c>
@@ -7190,7 +7197,7 @@
         <v>6693.4</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>45231</v>
       </c>
@@ -7234,7 +7241,7 @@
         <v>-1417.4</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>45261</v>
       </c>
@@ -7278,7 +7285,7 @@
         <v>-8430.1299999999992</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>45292</v>
       </c>
@@ -7322,7 +7329,7 @@
         <v>-16029.83</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>45323</v>
       </c>
@@ -7366,7 +7373,7 @@
         <v>-37447.24</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>45352</v>
       </c>
@@ -7410,7 +7417,7 @@
         <v>-42914.879999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>45383</v>
       </c>
@@ -7454,7 +7461,7 @@
         <v>-50038.43</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>45413</v>
       </c>
@@ -7498,7 +7505,7 @@
         <v>-56368.73</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>45444</v>
       </c>
@@ -7542,7 +7549,7 @@
         <v>-62702.64</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>45474</v>
       </c>
@@ -7586,7 +7593,7 @@
         <v>-69328.19</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>45505</v>
       </c>
@@ -7630,7 +7637,7 @@
         <v>-76096.55</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>45536</v>
       </c>
@@ -7674,7 +7681,7 @@
         <v>-82187.839999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>45566</v>
       </c>
@@ -7718,7 +7725,7 @@
         <v>-87605.58</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>45597</v>
       </c>
@@ -7762,7 +7769,7 @@
         <v>-92869.56</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>45627</v>
       </c>
@@ -7806,7 +7813,7 @@
         <v>-96420</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>45658</v>
       </c>
@@ -7850,7 +7857,7 @@
         <v>-99972.94</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>45689</v>
       </c>
@@ -7894,7 +7901,7 @@
         <v>-119101.8</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>45717</v>
       </c>
@@ -7938,7 +7945,7 @@
         <v>-123672.21</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>45748</v>
       </c>
@@ -7982,7 +7989,7 @@
         <v>-126605.31</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>45778</v>
       </c>
@@ -8026,7 +8033,7 @@
         <v>-130969.54</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>45809</v>
       </c>
@@ -8070,7 +8077,7 @@
         <v>-133867.51</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>45839</v>
       </c>
@@ -8114,7 +8121,7 @@
         <v>-134142.57999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>45870</v>
       </c>
@@ -8158,7 +8165,7 @@
         <v>-133550.16</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>45901</v>
       </c>
@@ -8202,7 +8209,7 @@
         <v>-133735.25</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>45931</v>
       </c>
@@ -8246,7 +8253,7 @@
         <v>-136015.48000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>45962</v>
       </c>
@@ -8290,7 +8297,7 @@
         <v>-134563.37</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>45992</v>
       </c>
@@ -8334,7 +8341,7 @@
         <v>-133346.57999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>46023</v>
       </c>
@@ -8377,6 +8384,24 @@
       <c r="N38" s="2">
         <v>-131998.44</v>
       </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="J40" s="2"/>
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="L41" s="2"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="J43" s="33"/>
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="J44" s="33"/>
+      <c r="L44" s="2"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="L46" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
